--- a/data/Field_Validation_URLs.xlsx
+++ b/data/Field_Validation_URLs.xlsx
@@ -1,34 +1,374 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="110">
+  <si>
+    <t>Pais</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Formulario</t>
+  </si>
+  <si>
+    <t>co</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>ar</t>
+  </si>
+  <si>
+    <t>py</t>
+  </si>
+  <si>
+    <t>ec</t>
+  </si>
+  <si>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>uy</t>
+  </si>
+  <si>
+    <t>bo</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/camionetas/traverse-camioneta-suv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/contacta-un-concesionario</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/convenioscorporativos/plan-educacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/flotas/portafolio</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/hibridos/captiva-phev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/lanzamiento-revelacion-sonic</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/ofertas-oportunidades</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/plan-chevrolet-siempre</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/servicios/colision</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/teleperformance</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/test-drive-auto-show</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/vehiculos-electricos/spark-euv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.co/vive-chevrolet</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/camionetas/tracker-turbo-suv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/colision</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/evento-chevydays</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/libro-reclamaciones-virtual</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/momentos-chevrolet</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/onstar/formulario-suscripcion-renovacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/oportunidades</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/pickups/montana</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/posventa</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/reactiva-tu-garantia</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/solicita-una-cotizacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/vehiculos-electricos</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/vehiculos-electricos/spark-euv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.pe/vehiculos-hibridos/captiva-phev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/airbag-takata</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/camionetas-pick-up/silverado-pickup/accesorios/formulario</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/camionetas-suv/tracker-suv/accesorios/formulario</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/eventos</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/financiamiento-autos-corporativos/autoescuela</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/formulario-reserva-de-servicios</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/formulario-verano-quote</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/hibridos/captiva-phev-test-drive</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/lanzamiento-revelacion-sonic</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/onix-test-drive</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/oportunidades</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/plan-chevrolet</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ar/solicita-una-cotizacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/autos/onix-plus-sedan-familiar</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/lanzamiento-revelacion-sonic</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/oportunidades</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/pickups/nueva-s10-high-country-4x4</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/pickups/silverado-camioneta-pickup</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/solicita-una-cotizacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/suvs/trailblazer-high-country-4x4</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/vehiculos-electricos</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/vehiculos-electricos/captiva-ev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/vehiculos-electricos/spark-euv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.py/vehiculos-electricos/spark-euv/accesorios/formulario</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/agenda-tu-mantenimiento</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/campanas-de-seguridad</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/evento</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/evento-aventura</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/evento-exhibicion-captiva-ev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/evento-exhibicion-test-drive-nevs</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/flotas-pesados-camiones</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/hibridos/captiva-phev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/ofertas-autos-suvs-camionetas</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/posventa/colision</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/socios-de-negocio/issfa</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/solicitar-cotizacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/suvs/groove-suv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/suvs/tracker-turbo-suv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/vehiculos-electricos/captiva-ev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.ec/vehiculos-electricos/equinox-ev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/autos-electricos/captiva-ev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/camiones/camion-mediano-ftr1524amt/serie-f</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/camiones/frr-camion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/camiones/fvz-camion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/evento-drive-experience</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/evento-maitencillo</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/flotas</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/flotas/planes-leasing</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/ofertas-oportunidades-descuentos</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/onstar/formulario-suscripcion-renovacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/pickups/colorado-camioneta-pickup/test-drive</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/solicitar-cotizacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/suvs/groove-suv-deportivo</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.cl/suvs/traverse</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/autos/onix-plus-auto-familiar</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/lanzamiento-revelacion-sonic</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/onstar/formulario-suscripcion-renovacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/pickups/silverado-camioneta-pickup</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/solicita-una-cotizacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/vans/n400-max</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/vehiculos-electricos</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/vehiculos-electricos/blazer-rs-ev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/vehiculos-electricos/captiva-ev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/vehiculos-electricos/spark-euv</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.uy/vehiculos-hibridos/captiva-phev</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.bo/autos/onix</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.bo/pickups/montana</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.bo/pickups/silverado</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.bo/solicitar-cotizacion</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.bo/suvs/suburban</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.bo/suvs/tahoe</t>
+  </si>
+  <si>
+    <t>https://www.chevrolet.com.bo/suvs/tracker</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -43,84 +383,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,32 +687,933 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C102"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Formulario</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3">
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3">
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3">
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3">
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3">
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3">
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3">
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3">
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3">
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3">
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3">
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3">
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3">
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3">
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3">
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3">
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3">
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3">
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3">
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3">
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3">
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3">
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3">
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3">
+      <c r="B72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3">
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3">
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3">
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3">
+      <c r="B76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3">
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="B78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3">
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3">
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="B86" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="B87" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="B88" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="B89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="B90" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="B91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="B92" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="B93" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="B94" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3">
+      <c r="B95" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3">
+      <c r="B96" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3">
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3">
+      <c r="B98" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3">
+      <c r="B99" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3">
+      <c r="B100" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="B101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3">
+      <c r="B102" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
+    <hyperlink ref="C17" r:id="rId16"/>
+    <hyperlink ref="C18" r:id="rId17"/>
+    <hyperlink ref="C19" r:id="rId18"/>
+    <hyperlink ref="C20" r:id="rId19"/>
+    <hyperlink ref="C21" r:id="rId20"/>
+    <hyperlink ref="C22" r:id="rId21"/>
+    <hyperlink ref="C23" r:id="rId22"/>
+    <hyperlink ref="C24" r:id="rId23"/>
+    <hyperlink ref="C25" r:id="rId24"/>
+    <hyperlink ref="C26" r:id="rId25"/>
+    <hyperlink ref="C27" r:id="rId26"/>
+    <hyperlink ref="C28" r:id="rId27"/>
+    <hyperlink ref="C29" r:id="rId28"/>
+    <hyperlink ref="C30" r:id="rId29"/>
+    <hyperlink ref="C31" r:id="rId30"/>
+    <hyperlink ref="C32" r:id="rId31"/>
+    <hyperlink ref="C33" r:id="rId32"/>
+    <hyperlink ref="C34" r:id="rId33"/>
+    <hyperlink ref="C35" r:id="rId34"/>
+    <hyperlink ref="C36" r:id="rId35"/>
+    <hyperlink ref="C37" r:id="rId36"/>
+    <hyperlink ref="C38" r:id="rId37"/>
+    <hyperlink ref="C39" r:id="rId38"/>
+    <hyperlink ref="C40" r:id="rId39"/>
+    <hyperlink ref="C41" r:id="rId40"/>
+    <hyperlink ref="C42" r:id="rId41"/>
+    <hyperlink ref="C43" r:id="rId42"/>
+    <hyperlink ref="C44" r:id="rId43"/>
+    <hyperlink ref="C45" r:id="rId44"/>
+    <hyperlink ref="C46" r:id="rId45"/>
+    <hyperlink ref="C47" r:id="rId46"/>
+    <hyperlink ref="C48" r:id="rId47"/>
+    <hyperlink ref="C49" r:id="rId48"/>
+    <hyperlink ref="C50" r:id="rId49"/>
+    <hyperlink ref="C51" r:id="rId50"/>
+    <hyperlink ref="C52" r:id="rId51"/>
+    <hyperlink ref="C53" r:id="rId52"/>
+    <hyperlink ref="C54" r:id="rId53"/>
+    <hyperlink ref="C55" r:id="rId54"/>
+    <hyperlink ref="C56" r:id="rId55"/>
+    <hyperlink ref="C57" r:id="rId56"/>
+    <hyperlink ref="C58" r:id="rId57"/>
+    <hyperlink ref="C59" r:id="rId58"/>
+    <hyperlink ref="C60" r:id="rId59"/>
+    <hyperlink ref="C61" r:id="rId60"/>
+    <hyperlink ref="C62" r:id="rId61"/>
+    <hyperlink ref="C63" r:id="rId62"/>
+    <hyperlink ref="C64" r:id="rId63"/>
+    <hyperlink ref="C65" r:id="rId64"/>
+    <hyperlink ref="C66" r:id="rId65"/>
+    <hyperlink ref="C67" r:id="rId66"/>
+    <hyperlink ref="C68" r:id="rId67"/>
+    <hyperlink ref="C69" r:id="rId68"/>
+    <hyperlink ref="C70" r:id="rId69"/>
+    <hyperlink ref="C71" r:id="rId70"/>
+    <hyperlink ref="C72" r:id="rId71"/>
+    <hyperlink ref="C73" r:id="rId72"/>
+    <hyperlink ref="C74" r:id="rId73"/>
+    <hyperlink ref="C75" r:id="rId74"/>
+    <hyperlink ref="C76" r:id="rId75"/>
+    <hyperlink ref="C77" r:id="rId76"/>
+    <hyperlink ref="C78" r:id="rId77"/>
+    <hyperlink ref="C79" r:id="rId78"/>
+    <hyperlink ref="C80" r:id="rId79"/>
+    <hyperlink ref="C81" r:id="rId80"/>
+    <hyperlink ref="C82" r:id="rId81"/>
+    <hyperlink ref="C83" r:id="rId82"/>
+    <hyperlink ref="C84" r:id="rId83"/>
+    <hyperlink ref="C85" r:id="rId84"/>
+    <hyperlink ref="C86" r:id="rId85"/>
+    <hyperlink ref="C87" r:id="rId86"/>
+    <hyperlink ref="C88" r:id="rId87"/>
+    <hyperlink ref="C89" r:id="rId88"/>
+    <hyperlink ref="C90" r:id="rId89"/>
+    <hyperlink ref="C91" r:id="rId90"/>
+    <hyperlink ref="C92" r:id="rId91"/>
+    <hyperlink ref="C93" r:id="rId92"/>
+    <hyperlink ref="C94" r:id="rId93"/>
+    <hyperlink ref="C95" r:id="rId94"/>
+    <hyperlink ref="C96" r:id="rId95"/>
+    <hyperlink ref="C97" r:id="rId96"/>
+    <hyperlink ref="C98" r:id="rId97"/>
+    <hyperlink ref="C99" r:id="rId98"/>
+    <hyperlink ref="C100" r:id="rId99"/>
+    <hyperlink ref="C101" r:id="rId100"/>
+    <hyperlink ref="C102" r:id="rId101"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>